--- a/data/raw/male_life_table_south_brazil_2025.xlsx
+++ b/data/raw/male_life_table_south_brazil_2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/Projeto IC - Vanessa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/projeto_longevidade/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75429AD5-326A-4909-AA89-15AF5647B461}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{114C36A1-5B6D-4163-B11C-ACC7BF477504}"/>
   <bookViews>
-    <workbookView xWindow="2772" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -516,31 +516,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>1.04019684734586E-2</v>
+        <v>1.07240661627779E-2</v>
       </c>
       <c r="C2" s="4">
-        <v>7.2119775776886205E-2</v>
+        <v>7.3028212107136101E-2</v>
       </c>
       <c r="D2" s="4">
-        <v>1.0302530705001501E-2</v>
+        <v>1.0618508559003601E-2</v>
       </c>
       <c r="E2" s="5">
         <v>100000</v>
       </c>
       <c r="F2" s="5">
-        <v>1030.25307050016</v>
+        <v>1061.8508559003501</v>
       </c>
       <c r="G2" s="5">
-        <v>99044.048549937797</v>
+        <v>99015.694213630501</v>
       </c>
       <c r="H2" s="6">
-        <v>0.98902024216876405</v>
+        <v>0.98868125491177095</v>
       </c>
       <c r="I2" s="5">
-        <v>7435522.5278171301</v>
+        <v>7393179.2514705602</v>
       </c>
       <c r="J2" s="7">
-        <v>74.355225278171304</v>
+        <v>73.931792514705606</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -548,31 +548,31 @@
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>4.3906507338178002E-4</v>
+        <v>4.54727416176636E-4</v>
       </c>
       <c r="C3" s="4">
-        <v>1.6219404230661201</v>
+        <v>1.62098778475898</v>
       </c>
       <c r="D3" s="4">
-        <v>1.7544284545966101E-3</v>
+        <v>1.8169440908140601E-3</v>
       </c>
       <c r="E3" s="5">
-        <v>98969.746929499801</v>
+        <v>98938.149144099603</v>
       </c>
       <c r="F3" s="5">
-        <v>173.63534015734299</v>
+        <v>179.765085443461</v>
       </c>
       <c r="G3" s="5">
-        <v>395466.07253444399</v>
+        <v>395324.93324225501</v>
       </c>
       <c r="H3" s="6">
-        <v>0.99836081750437899</v>
+        <v>0.99830404195240796</v>
       </c>
       <c r="I3" s="5">
-        <v>7336478.4792671902</v>
+        <v>7294163.5572569296</v>
       </c>
       <c r="J3" s="7">
-        <v>74.1284958977743</v>
+        <v>73.724479590104906</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -580,31 +580,31 @@
         <v>5</v>
       </c>
       <c r="B4" s="4">
-        <v>2.17630620942467E-4</v>
+        <v>2.24472946192967E-4</v>
       </c>
       <c r="C4" s="4">
-        <v>2.3844156619860102</v>
+        <v>2.38509400923459</v>
       </c>
       <c r="D4" s="4">
-        <v>1.0875340463546599E-3</v>
+        <v>1.1217063166685201E-3</v>
       </c>
       <c r="E4" s="5">
-        <v>98796.111589342501</v>
+        <v>98758.3840586562</v>
       </c>
       <c r="F4" s="5">
-        <v>107.44413500085599</v>
+        <v>110.777903222566</v>
       </c>
       <c r="G4" s="5">
-        <v>493699.52874999301</v>
+        <v>493502.24649049999</v>
       </c>
       <c r="H4" s="6">
-        <v>0.99891618669595095</v>
+        <v>0.99887844652737401</v>
       </c>
       <c r="I4" s="5">
-        <v>6941012.4067327501</v>
+        <v>6898838.62401467</v>
       </c>
       <c r="J4" s="7">
-        <v>70.255927030649502</v>
+        <v>69.855726070985597</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -612,31 +612,31 @@
         <v>10</v>
       </c>
       <c r="B5" s="4">
-        <v>2.5973205516873897E-4</v>
+        <v>2.6984813268101699E-4</v>
       </c>
       <c r="C5" s="4">
-        <v>2.8227395008655298</v>
+        <v>2.82535998874584</v>
       </c>
       <c r="D5" s="4">
-        <v>1.29792629288678E-3</v>
+        <v>1.3484493629163899E-3</v>
       </c>
       <c r="E5" s="5">
-        <v>98688.667454341601</v>
+        <v>98647.606155433605</v>
       </c>
       <c r="F5" s="5">
-        <v>128.09061629895601</v>
+        <v>133.021301673507</v>
       </c>
       <c r="G5" s="5">
-        <v>493164.45063253102</v>
+        <v>492948.75733220001</v>
       </c>
       <c r="H5" s="6">
-        <v>0.99711147654802501</v>
+        <v>0.996987241463831</v>
       </c>
       <c r="I5" s="5">
-        <v>6447312.8779827598</v>
+        <v>6405336.3775241701</v>
       </c>
       <c r="J5" s="7">
-        <v>65.329819971128998</v>
+        <v>64.931493293731194</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -644,31 +644,31 @@
         <v>15</v>
       </c>
       <c r="B6" s="4">
-        <v>1.02715297390363E-3</v>
+        <v>1.0729655332842199E-3</v>
       </c>
       <c r="C6" s="4">
-        <v>2.89553120099036</v>
+        <v>2.8963530805392601</v>
       </c>
       <c r="D6" s="4">
-        <v>5.1246872871316997E-3</v>
+        <v>5.35274576642267E-3</v>
       </c>
       <c r="E6" s="5">
-        <v>98560.576838042703</v>
+        <v>98514.584853760098</v>
       </c>
       <c r="F6" s="5">
-        <v>505.09213513426897</v>
+        <v>527.32352700685396</v>
       </c>
       <c r="G6" s="5">
-        <v>491739.93355119799</v>
+        <v>491463.621755653</v>
       </c>
       <c r="H6" s="6">
-        <v>0.99291058368920804</v>
+        <v>0.99259902724375804</v>
       </c>
       <c r="I6" s="5">
-        <v>5954148.4273502296</v>
+        <v>5912387.6201919699</v>
       </c>
       <c r="J6" s="7">
-        <v>60.411054991431698</v>
+        <v>60.015353350659801</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -676,31 +676,31 @@
         <v>20</v>
       </c>
       <c r="B7" s="4">
-        <v>1.7519274083994099E-3</v>
+        <v>1.82819381320192E-3</v>
       </c>
       <c r="C7" s="4">
-        <v>2.6342364829878302</v>
+        <v>2.6341145541435802</v>
       </c>
       <c r="D7" s="4">
-        <v>8.7234813005787407E-3</v>
+        <v>9.1016019332451001E-3</v>
       </c>
       <c r="E7" s="5">
-        <v>98055.484702908405</v>
+        <v>97987.261326753302</v>
       </c>
       <c r="F7" s="5">
-        <v>855.38518722502295</v>
+        <v>891.84104712496605</v>
       </c>
       <c r="G7" s="5">
-        <v>488253.78444561199</v>
+        <v>487826.31288035598</v>
       </c>
       <c r="H7" s="6">
-        <v>0.99050697508078001</v>
+        <v>0.99009026986123605</v>
       </c>
       <c r="I7" s="5">
-        <v>5462408.4937990298</v>
+        <v>5420923.9984363196</v>
       </c>
       <c r="J7" s="7">
-        <v>55.707322342541097</v>
+        <v>55.322742211963998</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -708,31 +708,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="4">
-        <v>1.9910164046971499E-3</v>
+        <v>2.0801877193555498E-3</v>
       </c>
       <c r="C8" s="4">
-        <v>2.5264970600359602</v>
+        <v>2.5266442737900601</v>
       </c>
       <c r="D8" s="4">
-        <v>9.9062956479612496E-3</v>
+        <v>1.0347699226812401E-2</v>
       </c>
       <c r="E8" s="5">
-        <v>97200.099515683396</v>
+        <v>97095.420279628306</v>
       </c>
       <c r="F8" s="5">
-        <v>962.89292281361099</v>
+        <v>1004.71420535452</v>
       </c>
       <c r="G8" s="5">
-        <v>483618.779102967</v>
+        <v>482992.08576512302</v>
       </c>
       <c r="H8" s="6">
-        <v>0.99001817375294299</v>
+        <v>0.989570961731285</v>
       </c>
       <c r="I8" s="5">
-        <v>4974154.70935342</v>
+        <v>4933097.6855559601</v>
       </c>
       <c r="J8" s="7">
-        <v>51.174378772635201</v>
+        <v>50.806697899334203</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -740,31 +740,31 @@
         <v>30</v>
       </c>
       <c r="B9" s="4">
-        <v>2.02954698959117E-3</v>
+        <v>2.1212867954342801E-3</v>
       </c>
       <c r="C9" s="4">
-        <v>2.5356802220114201</v>
+        <v>2.5356168756149202</v>
       </c>
       <c r="D9" s="4">
-        <v>1.0097234108285899E-2</v>
+        <v>1.0551275460825699E-2</v>
       </c>
       <c r="E9" s="5">
-        <v>96237.206592869799</v>
+        <v>96090.706074273796</v>
       </c>
       <c r="F9" s="5">
-        <v>971.72960489569198</v>
+        <v>1013.87950901491</v>
       </c>
       <c r="G9" s="5">
-        <v>478791.38048014703</v>
+        <v>477954.94281919301</v>
       </c>
       <c r="H9" s="6">
-        <v>0.98911875533509996</v>
+        <v>0.98862824224943002</v>
       </c>
       <c r="I9" s="5">
-        <v>4490535.93025045</v>
+        <v>4450105.5997908404</v>
       </c>
       <c r="J9" s="7">
-        <v>46.661120882774597</v>
+        <v>46.311509006408102</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -772,31 +772,31 @@
         <v>35</v>
       </c>
       <c r="B10" s="4">
-        <v>2.4113959206954099E-3</v>
+        <v>2.5209404093852099E-3</v>
       </c>
       <c r="C10" s="4">
-        <v>2.5955617730918399</v>
+        <v>2.5953728067569402</v>
       </c>
       <c r="D10" s="4">
-        <v>1.1987475590279399E-2</v>
+        <v>1.25287537208551E-2</v>
       </c>
       <c r="E10" s="5">
-        <v>95265.476987974107</v>
+        <v>95076.826565258903</v>
       </c>
       <c r="F10" s="5">
-        <v>1141.99257998966</v>
+        <v>1191.1941445965799</v>
       </c>
       <c r="G10" s="5">
-        <v>473581.53432569798</v>
+        <v>472519.75499376497</v>
       </c>
       <c r="H10" s="6">
-        <v>0.98601030572552395</v>
+        <v>0.98537685778028805</v>
       </c>
       <c r="I10" s="5">
-        <v>4011744.5497702998</v>
+        <v>3972150.6569716502</v>
       </c>
       <c r="J10" s="7">
-        <v>42.111210446956797</v>
+        <v>41.778326017699399</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -804,31 +804,31 @@
         <v>40</v>
       </c>
       <c r="B11" s="4">
-        <v>3.2891299613320699E-3</v>
+        <v>3.43845334081556E-3</v>
       </c>
       <c r="C11" s="4">
-        <v>2.6162532852435798</v>
+        <v>2.6151266221492899</v>
       </c>
       <c r="D11" s="4">
-        <v>1.6317711560350799E-2</v>
+        <v>1.7052432057573799E-2</v>
       </c>
       <c r="E11" s="5">
-        <v>94123.484407984404</v>
+        <v>93885.632420662296</v>
       </c>
       <c r="F11" s="5">
-        <v>1535.8798696246499</v>
+        <v>1600.97836803569</v>
       </c>
       <c r="G11" s="5">
-        <v>466956.27344644401</v>
+        <v>465610.03141486802</v>
       </c>
       <c r="H11" s="6">
-        <v>0.98129543203509195</v>
+        <v>0.98049275485117104</v>
       </c>
       <c r="I11" s="5">
-        <v>3538163.0154446</v>
+        <v>3499630.9019778799</v>
       </c>
       <c r="J11" s="7">
-        <v>37.5906505979762</v>
+        <v>37.275468160000202</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -836,31 +836,31 @@
         <v>45</v>
       </c>
       <c r="B12" s="4">
-        <v>4.3540779634003096E-3</v>
+        <v>4.5340896737787696E-3</v>
       </c>
       <c r="C12" s="4">
-        <v>2.6362674075958901</v>
+        <v>2.6347051559974002</v>
       </c>
       <c r="D12" s="4">
-        <v>2.1548614152347E-2</v>
+        <v>2.2429899829422301E-2</v>
       </c>
       <c r="E12" s="5">
-        <v>92587.604538359796</v>
+        <v>92284.654052626604</v>
       </c>
       <c r="F12" s="5">
-        <v>1995.13456548721</v>
+        <v>2069.9355461933001</v>
       </c>
       <c r="G12" s="5">
-        <v>458222.058093125</v>
+        <v>456527.26238830399</v>
       </c>
       <c r="H12" s="6">
-        <v>0.97342473926486695</v>
+        <v>0.97236842642655197</v>
       </c>
       <c r="I12" s="5">
-        <v>3071206.7419981598</v>
+        <v>3034020.87056302</v>
       </c>
       <c r="J12" s="7">
-        <v>33.170819758337501</v>
+        <v>32.876764850121504</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -868,31 +868,31 @@
         <v>50</v>
       </c>
       <c r="B13" s="4">
-        <v>6.6077778443393896E-3</v>
+        <v>6.8685114277819504E-3</v>
       </c>
       <c r="C13" s="4">
-        <v>2.65293259914798</v>
+        <v>2.65140991651703</v>
       </c>
       <c r="D13" s="4">
-        <v>3.2534317742223602E-2</v>
+        <v>3.3797361164235998E-2</v>
       </c>
       <c r="E13" s="5">
-        <v>90592.469972872597</v>
+        <v>90214.718506433303</v>
       </c>
       <c r="F13" s="5">
-        <v>2947.36420315028</v>
+        <v>3049.0194236918201</v>
       </c>
       <c r="G13" s="5">
-        <v>446044.68742471101</v>
+        <v>443912.69574933703</v>
       </c>
       <c r="H13" s="6">
-        <v>0.96050624462380896</v>
+        <v>0.959042662051939</v>
       </c>
       <c r="I13" s="5">
-        <v>2612984.6839050301</v>
+        <v>2577493.6081747101</v>
       </c>
       <c r="J13" s="7">
-        <v>28.843287799609399</v>
+        <v>28.570655108688399</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -900,31 +900,31 @@
         <v>55</v>
       </c>
       <c r="B14" s="4">
-        <v>9.6916735809412496E-3</v>
+        <v>1.0045020544602301E-2</v>
       </c>
       <c r="C14" s="4">
-        <v>2.6405659676927402</v>
+        <v>2.6388794450127699</v>
       </c>
       <c r="D14" s="4">
-        <v>4.7375049077857001E-2</v>
+        <v>4.9061486692434597E-2</v>
       </c>
       <c r="E14" s="5">
-        <v>87645.1057697223</v>
+        <v>87165.699082741499</v>
       </c>
       <c r="F14" s="5">
-        <v>4152.1911872745704</v>
+        <v>4276.4787855846798</v>
       </c>
       <c r="G14" s="5">
-        <v>428428.70765271003</v>
+        <v>425731.21345009701</v>
       </c>
       <c r="H14" s="6">
-        <v>0.94261628200759495</v>
+        <v>0.940638540880121</v>
       </c>
       <c r="I14" s="5">
-        <v>2166939.9964803201</v>
+        <v>2133580.91242537</v>
       </c>
       <c r="J14" s="7">
-        <v>24.724027399473002</v>
+        <v>24.477299383557799</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -932,31 +932,31 @@
         <v>60</v>
       </c>
       <c r="B15" s="4">
-        <v>1.4294585042411399E-2</v>
+        <v>1.4791000878522E-2</v>
       </c>
       <c r="C15" s="4">
-        <v>2.6405309173664802</v>
+        <v>2.6386189063067498</v>
       </c>
       <c r="D15" s="4">
-        <v>6.9140964251234199E-2</v>
+        <v>7.1459137530884898E-2</v>
       </c>
       <c r="E15" s="5">
-        <v>83492.914582447702</v>
+        <v>82889.220297156804</v>
       </c>
       <c r="F15" s="5">
-        <v>5772.7806223763801</v>
+        <v>5923.1921930423396</v>
       </c>
       <c r="G15" s="5">
-        <v>403843.87551291601</v>
+        <v>400459.18742682203</v>
       </c>
       <c r="H15" s="6">
-        <v>0.91448533590283498</v>
+        <v>0.91175483857039397</v>
       </c>
       <c r="I15" s="5">
-        <v>1738511.28882761</v>
+        <v>1707849.6989752799</v>
       </c>
       <c r="J15" s="7">
-        <v>20.822261356212</v>
+        <v>20.604002460786301</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -964,31 +964,31 @@
         <v>65</v>
       </c>
       <c r="B16" s="4">
-        <v>2.19498735118023E-2</v>
+        <v>2.26544840260153E-2</v>
       </c>
       <c r="C16" s="4">
-        <v>2.6201984170272001</v>
+        <v>2.6172090235677499</v>
       </c>
       <c r="D16" s="4">
-        <v>0.10430106146118</v>
+        <v>0.107471036826133</v>
       </c>
       <c r="E16" s="5">
-        <v>77720.133960071296</v>
+        <v>76966.028104114404</v>
       </c>
       <c r="F16" s="5">
-        <v>8106.2924689405299</v>
+        <v>8271.6188407384907</v>
       </c>
       <c r="G16" s="5">
-        <v>369309.30215073202</v>
+        <v>365120.601786374</v>
       </c>
       <c r="H16" s="6">
-        <v>0.87594433125140903</v>
+        <v>0.872522218214969</v>
       </c>
       <c r="I16" s="5">
-        <v>1334667.4133146999</v>
+        <v>1307390.51154846</v>
       </c>
       <c r="J16" s="7">
-        <v>17.172736912681899</v>
+        <v>16.986591925724799</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -996,31 +996,31 @@
         <v>70</v>
       </c>
       <c r="B17" s="4">
-        <v>3.1700483528714303E-2</v>
+        <v>3.2562688242947002E-2</v>
       </c>
       <c r="C17" s="4">
-        <v>2.6036090758497199</v>
+        <v>2.6000613753594402</v>
       </c>
       <c r="D17" s="4">
-        <v>0.14731163160330399</v>
+        <v>0.15101208068889099</v>
       </c>
       <c r="E17" s="5">
-        <v>69613.841491130806</v>
+        <v>68694.409263376001</v>
       </c>
       <c r="F17" s="5">
-        <v>10254.9285722322</v>
+        <v>10373.6856745566</v>
       </c>
       <c r="G17" s="5">
-        <v>323494.38969734701</v>
+        <v>318575.837386631</v>
       </c>
       <c r="H17" s="6">
-        <v>0.81970537255793896</v>
+        <v>0.815619736959738</v>
       </c>
       <c r="I17" s="5">
-        <v>965358.11116396706</v>
+        <v>942269.90976208204</v>
       </c>
       <c r="J17" s="7">
-        <v>13.8673299804459</v>
+        <v>13.716835472729599</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1028,31 +1028,31 @@
         <v>75</v>
       </c>
       <c r="B18" s="4">
-        <v>4.9555327681113599E-2</v>
+        <v>5.07179193360765E-2</v>
       </c>
       <c r="C18" s="4">
-        <v>2.5933748962638501</v>
+        <v>2.5894700248934801</v>
       </c>
       <c r="D18" s="4">
-        <v>0.22137519062792099</v>
+        <v>0.225963912036274</v>
       </c>
       <c r="E18" s="5">
-        <v>59358.912918898597</v>
+        <v>58320.723588819303</v>
       </c>
       <c r="F18" s="5">
-        <v>13140.5906628874</v>
+        <v>13178.3788549158</v>
       </c>
       <c r="G18" s="5">
-        <v>265170.08922726702</v>
+        <v>259836.740691012</v>
       </c>
       <c r="H18" s="6">
-        <v>0.72568491060227502</v>
+        <v>0.72070110273637999</v>
       </c>
       <c r="I18" s="5">
-        <v>641863.72146661999</v>
+        <v>623694.07237545098</v>
       </c>
       <c r="J18" s="7">
-        <v>10.813266111250901</v>
+        <v>10.694210119419999</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1060,31 +1060,31 @@
         <v>80</v>
       </c>
       <c r="B19" s="4">
-        <v>8.1457768897850794E-2</v>
+        <v>8.3079868261135101E-2</v>
       </c>
       <c r="C19" s="4">
-        <v>2.53353151891843</v>
+        <v>2.5287765277718899</v>
       </c>
       <c r="D19" s="4">
-        <v>0.33914932877494097</v>
+        <v>0.34464138963449797</v>
       </c>
       <c r="E19" s="5">
-        <v>46218.322256011197</v>
+        <v>45142.344733903497</v>
       </c>
       <c r="F19" s="5">
-        <v>15674.9129702301</v>
+        <v>15557.920420452099</v>
       </c>
       <c r="G19" s="5">
-        <v>192429.93249528701</v>
+        <v>187264.62554743901</v>
       </c>
       <c r="H19" s="6">
-        <v>0.59349614477551205</v>
+        <v>0.58783382168391596</v>
       </c>
       <c r="I19" s="5">
-        <v>376693.63223935303</v>
+        <v>363857.33168443898</v>
       </c>
       <c r="J19" s="7">
-        <v>8.1503095277405908</v>
+        <v>8.0602222553842804</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1092,31 +1092,31 @@
         <v>85</v>
       </c>
       <c r="B20" s="4">
-        <v>0.13144897534088401</v>
+        <v>0.13364744197221101</v>
       </c>
       <c r="C20" s="4">
-        <v>2.4347315868654298</v>
+        <v>2.4278339912309099</v>
       </c>
       <c r="D20" s="4">
-        <v>0.491507583522866</v>
+        <v>0.497287845599302</v>
       </c>
       <c r="E20" s="5">
-        <v>30543.409285781101</v>
+        <v>29584.424313451502</v>
       </c>
       <c r="F20" s="5">
-        <v>15012.3172906041</v>
+        <v>14711.974630131899</v>
       </c>
       <c r="G20" s="5">
-        <v>114206.423075365</v>
+        <v>110080.480501759</v>
       </c>
       <c r="H20" s="6">
-        <v>0.38020118322820901</v>
+        <v>0.37664197514273801</v>
       </c>
       <c r="I20" s="5">
-        <v>184263.69974406599</v>
+        <v>176592.70613699901</v>
       </c>
       <c r="J20" s="7">
-        <v>6.0328464979135896</v>
+        <v>5.9691107816049698</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1124,31 +1124,31 @@
         <v>90</v>
       </c>
       <c r="B21" s="4">
-        <v>0.221691346476727</v>
+        <v>0.22360475147654099</v>
       </c>
       <c r="C21" s="4">
-        <v>4.5107759770180298</v>
+        <v>4.4721768808428601</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
       <c r="E21" s="5">
-        <v>15531.091995176999</v>
+        <v>14872.449683319601</v>
       </c>
       <c r="F21" s="5">
-        <v>15531.091995176999</v>
+        <v>14872.449683319601</v>
       </c>
       <c r="G21" s="5">
-        <v>70057.276668701306</v>
+        <v>66512.225635240495</v>
       </c>
       <c r="H21" s="6">
         <v>0</v>
       </c>
       <c r="I21" s="5">
-        <v>70057.276668701306</v>
+        <v>66512.225635240495</v>
       </c>
       <c r="J21" s="7">
-        <v>4.5107759770180298</v>
+        <v>4.4721768808428601</v>
       </c>
     </row>
   </sheetData>
